--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2916,13 +2916,24 @@
       <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="0" t="n">
+        <v>3662.1765</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" t="n">
+        <v>15</v>
+      </c>
+      <c r="F42" t="n">
         <v>3662.1765</v>
       </c>
     </row>

--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2927,13 +2927,24 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="0" t="n">
+        <v>3662.1765</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="n">
+        <v>16</v>
+      </c>
+      <c r="F43" t="n">
         <v>3662.1765</v>
       </c>
     </row>

--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2938,13 +2938,24 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="0" t="n">
+        <v>3662.1765</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" t="n">
         <v>3662.1765</v>
       </c>
     </row>

--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2949,13 +2949,24 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="0" t="n">
+        <v>3662.1765</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" t="n">
+        <v>18</v>
+      </c>
+      <c r="F45" t="n">
         <v>3662.1765</v>
       </c>
     </row>

--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2960,14 +2960,25 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="0" t="n">
         <v>3662.1765</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3687.8274</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Shipping Indices/2025~2026_Drewry World Container Index_USD.xlsx
@@ -2183,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1">
@@ -2971,13 +2971,24 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="0" t="n">
+        <v>3687.8274</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" t="n">
+        <v>23</v>
+      </c>
+      <c r="F47" t="n">
         <v>3687.8274</v>
       </c>
     </row>
